--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486928_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486928_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3625</v>
+        <v>12.0834</v>
       </c>
       <c r="E2" t="n">
-        <v>10.4889</v>
+        <v>9.5359</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8736</v>
+        <v>2.5475</v>
       </c>
       <c r="G2" t="n">
         <v>3.6535</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1731</v>
+        <v>0.8941</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5378</v>
+        <v>0.5848</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6353</v>
+        <v>0.3092</v>
       </c>
       <c r="V2" t="n">
         <v>5.8932</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.96</v>
+        <v>7.4087</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5264</v>
+        <v>5.6194</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4336</v>
+        <v>1.7893</v>
       </c>
       <c r="G3" t="n">
         <v>6.307</v>
@@ -688,13 +688,13 @@
         <v>2.4641</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2744</v>
+        <v>0.1743</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1431</v>
+        <v>0.2361</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4175</v>
+        <v>-0.0618</v>
       </c>
       <c r="V3" t="n">
         <v>-1.5367</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0011</v>
+        <v>5.4919</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8845</v>
+        <v>1.4346</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1166</v>
+        <v>4.0573</v>
       </c>
       <c r="G4" t="n">
         <v>2.4021</v>
@@ -766,13 +766,13 @@
         <v>2.4641</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3403</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0931</v>
+        <v>0.457</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4334</v>
+        <v>0.3741</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.8091</v>
+        <v>5.2803</v>
       </c>
       <c r="E5" t="n">
-        <v>1.056</v>
+        <v>2.0905</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7531</v>
+        <v>3.1898</v>
       </c>
       <c r="G5" t="n">
         <v>2.0004</v>
@@ -844,13 +844,13 @@
         <v>2.6694</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3105</v>
+        <v>0.7817</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1198</v>
+        <v>-0.0854</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4303</v>
+        <v>0.8671</v>
       </c>
       <c r="V5" t="n">
         <v>1.0608</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8701</v>
+        <v>0.8998</v>
       </c>
       <c r="E6" t="n">
         <v>0.0789</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7913</v>
+        <v>0.8209</v>
       </c>
       <c r="G6" t="n">
         <v>0.1608</v>
@@ -922,13 +922,13 @@
         <v>1.0267</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3173</v>
+        <v>-0.2877</v>
       </c>
       <c r="T6" t="n">
         <v>-0.1976</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4021</v>
+        <v>0.0418</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6179</v>
+        <v>-0.3815</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2158</v>
+        <v>0.4233</v>
       </c>
       <c r="G7" t="n">
         <v>1.501</v>
@@ -1000,13 +1000,13 @@
         <v>1.6427</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4041</v>
+        <v>0.0397</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2249</v>
+        <v>0.0115</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1792</v>
+        <v>0.0283</v>
       </c>
       <c r="V7" t="n">
         <v>0.3491</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7613</v>
+        <v>-1.7782</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4713</v>
+        <v>-1.3831</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.29</v>
+        <v>-0.3951</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0506</v>
+        <v>-1.9051</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.185</v>
+        <v>-1.2552</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8656</v>
+        <v>-0.6498</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9933</v>
+        <v>-1.3947</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9538</v>
+        <v>-1.3947</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0439</v>
+        <v>-0.5104</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1389</v>
+        <v>0.1395</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.905</v>
+        <v>-0.6498</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4641</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2552</v>
+        <v>-0.0785</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.0116</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2558</v>
+        <v>-0.0901</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1179</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0171</v>
+        <v>-2.3231</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5923</v>
+        <v>-1.0331</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4247</v>
+        <v>-1.29</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9051</v>
+        <v>-1.0506</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2552</v>
+        <v>-0.185</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6498</v>
+        <v>-0.8656</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3947</v>
+        <v>0.9933</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.3947</v>
+        <v>0.9538</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5104</v>
+        <v>-2.0439</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1395</v>
+        <v>-1.1389</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6498</v>
+        <v>-0.905</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.4641</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3173</v>
+        <v>0.6935</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1976</v>
+        <v>0.4377</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1197</v>
+        <v>0.2558</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1179</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1179</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2256</v>
+        <v>-2.5501</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.008</v>
+        <v>-1.7555</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2176</v>
+        <v>-0.7946</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0869</v>
+        <v>-2.8469</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2845</v>
+        <v>-1.9365</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8024</v>
+        <v>-0.9104</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7956</v>
+        <v>-2.5342</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4798</v>
+        <v>-1.9947</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3158</v>
+        <v>-0.5395</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2913</v>
+        <v>-0.3127</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8047</v>
+        <v>0.0582</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4866</v>
+        <v>-0.3709</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3254</v>
+        <v>0.9424</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8677</v>
+        <v>0.5385</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4577</v>
+        <v>0.404</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1786</v>
+        <v>-1.0563</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.928</v>
+        <v>-2.748</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.926</v>
+        <v>-0.0963</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.002</v>
+        <v>-2.6517</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8469</v>
+        <v>-2.5167</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9365</v>
+        <v>-0.3959</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9104</v>
+        <v>-2.1208</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.5342</v>
+        <v>-0.7518</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.9947</v>
+        <v>0.6034</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5395</v>
+        <v>-1.3552</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3127</v>
+        <v>-1.7649</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0582</v>
+        <v>-0.9994</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3709</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="P11" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5645</v>
+        <v>-0.2838</v>
       </c>
       <c r="T11" t="n">
-        <v>0.368</v>
+        <v>-0.3178</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1965</v>
+        <v>0.034</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0563</v>
+        <v>-0.3581</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2965</v>
+        <v>-1.5367</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2371</v>
+        <v>-3.0929</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4372</v>
+        <v>-2.6085</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7999</v>
+        <v>-0.4844</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5167</v>
+        <v>-3.0869</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3959</v>
+        <v>-1.2845</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.1208</v>
+        <v>-1.8024</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7518</v>
+        <v>-1.7956</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6034</v>
+        <v>-0.4798</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3552</v>
+        <v>-1.3158</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7649</v>
+        <v>-1.2913</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9994</v>
+        <v>-0.8047</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.4866</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4107</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R12" t="n">
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.773</v>
+        <v>0.4582</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6587</v>
+        <v>0.2673</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1143</v>
+        <v>0.1909</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3581</v>
+        <v>1.1786</v>
       </c>
       <c r="W12" t="n">
         <v>1.1786</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1441</v>
+        <v>-3.1089</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.596</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5481</v>
+        <v>-2.3109</v>
       </c>
       <c r="G13" t="n">
         <v>-0.396</v>
@@ -1468,13 +1468,13 @@
         <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1321</v>
+        <v>-0.0969</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5928</v>
+        <v>0.2052</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5393</v>
+        <v>-0.3021</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1786</v>
@@ -1501,22 +1501,22 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.2875</v>
+        <v>15.6047</v>
       </c>
       <c r="E14" t="n">
-        <v>9.385999999999997</v>
+        <v>10.7034</v>
       </c>
       <c r="F14" t="n">
-        <v>4.901700000000001</v>
+        <v>4.901400000000002</v>
       </c>
       <c r="G14" t="n">
         <v>4.222599999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0654</v>
+        <v>3.065399999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.157299999999998</v>
+        <v>1.157299999999999</v>
       </c>
       <c r="J14" t="n">
         <v>9.503500000000001</v>
@@ -1546,10 +1546,10 @@
         <v>16.4271</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7508</v>
+        <v>4.0681</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8316000000000003</v>
+        <v>2.1489</v>
       </c>
       <c r="U14" t="n">
         <v>1.9193</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.1006</v>
+        <v>4.472</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0678</v>
+        <v>1.1724</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0329</v>
+        <v>3.2997</v>
       </c>
       <c r="G15" t="n">
         <v>3.698</v>
@@ -1624,13 +1624,13 @@
         <v>1.8481</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4886</v>
+        <v>-0.1172</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3798</v>
+        <v>-0.2752</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1088</v>
+        <v>0.158</v>
       </c>
       <c r="V15" t="n">
         <v>0.0698</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3688</v>
+        <v>2.8772</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4902</v>
+        <v>1.1764</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8786</v>
+        <v>1.7007</v>
       </c>
       <c r="G16" t="n">
         <v>0.5893</v>
@@ -1702,13 +1702,13 @@
         <v>2.4641</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5556</v>
+        <v>0.0639</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1858</v>
+        <v>-0.128</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3698</v>
+        <v>0.1919</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8638</v>
+        <v>2.5377</v>
       </c>
       <c r="E17" t="n">
         <v>2.7709</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0929</v>
+        <v>-0.2332</v>
       </c>
       <c r="G17" t="n">
         <v>5.1705</v>
@@ -1780,13 +1780,13 @@
         <v>1.8481</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.2974</v>
       </c>
       <c r="T17" t="n">
         <v>0.2517</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3718</v>
+        <v>0.0457</v>
       </c>
       <c r="V17" t="n">
         <v>-1.6981</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0381</v>
+        <v>0.7696</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8426</v>
+        <v>1.6334</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8045</v>
+        <v>-0.8638</v>
       </c>
       <c r="G18" t="n">
         <v>0.6011</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.437</v>
+        <v>0.1685</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5656</v>
+        <v>0.3564</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1286</v>
+        <v>-0.1879</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9933</v>
+        <v>-0.9811</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3429</v>
+        <v>0.0291</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3363</v>
+        <v>-1.0102</v>
       </c>
       <c r="G19" t="n">
         <v>-0.1917</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1901</v>
+        <v>0.2024</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6042</v>
+        <v>0.2904</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4141</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0.2402</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.148</v>
+        <v>-1.0747</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3089</v>
+        <v>-2.4135</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1609</v>
+        <v>1.3388</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4955</v>
@@ -2014,13 +2014,13 @@
         <v>2.6694</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0713</v>
+        <v>0.0019</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2753</v>
+        <v>-0.3799</v>
       </c>
       <c r="U20" t="n">
-        <v>0.204</v>
+        <v>0.3818</v>
       </c>
       <c r="V20" t="n">
         <v>0.8295</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9321</v>
+        <v>-1.9757</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6906</v>
+        <v>-2.586</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.6103</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3522</v>
@@ -2170,13 +2170,13 @@
         <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.738</v>
+        <v>-0.7816</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7091</v>
+        <v>-0.6045</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0289</v>
+        <v>-0.1771</v>
       </c>
       <c r="V22" t="n">
         <v>-0.8686</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7121</v>
+        <v>-4.0992</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3583</v>
+        <v>-1.5676</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3538</v>
+        <v>-2.5316</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2183</v>
@@ -2248,13 +2248,13 @@
         <v>0.2053</v>
       </c>
       <c r="S23" t="n">
-        <v>0.079</v>
+        <v>-0.308</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.159</v>
+        <v>-0.3682</v>
       </c>
       <c r="U23" t="n">
-        <v>0.238</v>
+        <v>0.0602</v>
       </c>
       <c r="V23" t="n">
         <v>1.2484</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.211</v>
+        <v>-4.7943</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6938</v>
+        <v>-0.4846</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.5173</v>
+        <v>-4.3098</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9933</v>
@@ -2326,13 +2326,13 @@
         <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2177</v>
+        <v>-0.801</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4225</v>
+        <v>-0.2133</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7953</v>
+        <v>-0.5878</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7679</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.1108</v>
+        <v>-10.4675</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.1861</v>
+        <v>-4.4539</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.9247</v>
+        <v>-6.0137</v>
       </c>
       <c r="G25" t="n">
         <v>-4.9556</v>
@@ -2404,13 +2404,13 @@
         <v>0.616</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6439</v>
+        <v>-1.0006</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3833</v>
+        <v>-0.6511</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2606</v>
+        <v>-0.3495</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0472</v>
@@ -2440,10 +2440,10 @@
         <v>-14.2874</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9014</v>
+        <v>-4.9015</v>
       </c>
       <c r="F26" t="n">
-        <v>-9.385999999999999</v>
+        <v>-9.386100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-4.2226</v>
@@ -2488,7 +2488,7 @@
         <v>-1.9193</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8316000000000001</v>
+        <v>-0.8316</v>
       </c>
       <c r="V26" t="n">
         <v>-4.2341</v>
